--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104585_W15.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104585_W15.xlsx
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.6825</v>
+        <v>3.6109</v>
       </c>
       <c r="E2" t="n">
-        <v>4.4836</v>
+        <v>4.1498</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.8012</v>
+        <v>-0.5387999999999999</v>
       </c>
       <c r="G2" t="n">
-        <v>3.3035</v>
+        <v>3.2958</v>
       </c>
       <c r="H2" t="n">
-        <v>2.9915</v>
+        <v>2.9736</v>
       </c>
       <c r="I2" t="n">
-        <v>0.312</v>
+        <v>0.3222</v>
       </c>
       <c r="J2" t="n">
-        <v>5.8286</v>
+        <v>5.7899</v>
       </c>
       <c r="K2" t="n">
-        <v>5.0076</v>
+        <v>4.9707</v>
       </c>
       <c r="L2" t="n">
-        <v>0.821</v>
+        <v>0.8192</v>
       </c>
       <c r="M2" t="n">
-        <v>-2.5251</v>
+        <v>-2.4941</v>
       </c>
       <c r="N2" t="n">
-        <v>-2.0161</v>
+        <v>-1.9971</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.509</v>
+        <v>-0.497</v>
       </c>
       <c r="P2" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q2" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R2" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S2" t="n">
-        <v>0.9687</v>
+        <v>0.907</v>
       </c>
       <c r="T2" t="n">
-        <v>0.9648</v>
+        <v>0.6848</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0039</v>
+        <v>0.2221</v>
       </c>
       <c r="V2" t="n">
-        <v>0.7712</v>
+        <v>0.7739</v>
       </c>
       <c r="W2" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.3214</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="3">
@@ -643,58 +643,58 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.3992</v>
+        <v>3.2413</v>
       </c>
       <c r="E3" t="n">
-        <v>3.6747</v>
+        <v>3.4953</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.2755</v>
+        <v>-0.254</v>
       </c>
       <c r="G3" t="n">
-        <v>1.3396</v>
+        <v>1.3413</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3693</v>
+        <v>0.3732</v>
       </c>
       <c r="I3" t="n">
-        <v>0.9702</v>
+        <v>0.9681999999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>3.1485</v>
+        <v>3.1331</v>
       </c>
       <c r="K3" t="n">
-        <v>1.4719</v>
+        <v>1.4651</v>
       </c>
       <c r="L3" t="n">
-        <v>1.6765</v>
+        <v>1.668</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.8089</v>
+        <v>-1.7918</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.1026</v>
+        <v>-1.092</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.7063</v>
+        <v>-0.6998</v>
       </c>
       <c r="P3" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S3" t="n">
-        <v>0.4718</v>
+        <v>0.3066</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5263</v>
+        <v>0.3622</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0544</v>
+        <v>-0.0556</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.2577</v>
+        <v>2.8212</v>
       </c>
       <c r="E4" t="n">
-        <v>2.2109</v>
+        <v>2.7356</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0468</v>
+        <v>0.0857</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1864</v>
+        <v>0.1962</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.1863</v>
+        <v>-1.1726</v>
       </c>
       <c r="I4" t="n">
-        <v>1.3727</v>
+        <v>1.3688</v>
       </c>
       <c r="J4" t="n">
-        <v>1.8238</v>
+        <v>1.8021</v>
       </c>
       <c r="K4" t="n">
-        <v>1.1602</v>
+        <v>1.1549</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6636</v>
+        <v>0.6473</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.6374</v>
+        <v>-1.6059</v>
       </c>
       <c r="N4" t="n">
-        <v>-2.3466</v>
+        <v>-2.3274</v>
       </c>
       <c r="O4" t="n">
-        <v>0.7091</v>
+        <v>0.7215</v>
       </c>
       <c r="P4" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1905</v>
+        <v>0.7341</v>
       </c>
       <c r="T4" t="n">
-        <v>0.3871</v>
+        <v>0.9334</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1966</v>
+        <v>-0.1994</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. RODRIGUEZ</t>
+          <t>T. BELL-HAYNES</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.3789</v>
+        <v>1.5564</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5637</v>
+        <v>1.9166</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8151</v>
+        <v>-0.3602</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.5493</v>
+        <v>1.6181</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.4876</v>
+        <v>1.0519</v>
       </c>
       <c r="I5" t="n">
-        <v>0.9382</v>
+        <v>0.5662</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3954</v>
+        <v>3.6545</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.3055</v>
+        <v>3.1781</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7009</v>
+        <v>0.4764</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.9447</v>
+        <v>-2.0364</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.1821</v>
+        <v>-2.1262</v>
       </c>
       <c r="O5" t="n">
-        <v>0.2373</v>
+        <v>0.0898</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.9073</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R5" t="n">
-        <v>1.361</v>
+        <v>1.8211</v>
       </c>
       <c r="S5" t="n">
-        <v>2.2892</v>
+        <v>0.2358</v>
       </c>
       <c r="T5" t="n">
-        <v>1.8903</v>
+        <v>0.3807</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3989</v>
+        <v>-0.1449</v>
       </c>
       <c r="V5" t="n">
-        <v>0.5463</v>
+        <v>0.1578</v>
       </c>
       <c r="W5" t="n">
-        <v>0.5463</v>
+        <v>0.1578</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. FERNANDEZ</t>
+          <t>S. YUSTA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.311</v>
+        <v>1.3123</v>
       </c>
       <c r="E6" t="n">
-        <v>2.8178</v>
+        <v>-0.5226</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.5068</v>
+        <v>1.835</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1137</v>
+        <v>-0.5316</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2149</v>
+        <v>0.1952</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1012</v>
+        <v>-0.7268</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7154</v>
+        <v>0.415</v>
       </c>
       <c r="K6" t="n">
-        <v>0.6407</v>
+        <v>2.7094</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0746</v>
+        <v>-2.2945</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.6017</v>
+        <v>-0.9466</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.4258</v>
+        <v>-2.5142</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.1759</v>
+        <v>1.5677</v>
       </c>
       <c r="P6" t="n">
-        <v>1.1342</v>
+        <v>-2.5039</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-4.5526</v>
       </c>
       <c r="R6" t="n">
-        <v>1.1342</v>
+        <v>2.0487</v>
       </c>
       <c r="S6" t="n">
-        <v>1.7022</v>
+        <v>0.3055</v>
       </c>
       <c r="T6" t="n">
-        <v>1.9417</v>
+        <v>0.7336</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2395</v>
+        <v>-0.4281</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.639</v>
+        <v>4.0424</v>
       </c>
       <c r="W6" t="n">
-        <v>0.1607</v>
+        <v>2.8814</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.7997</v>
+        <v>1.1609</v>
       </c>
     </row>
     <row r="7">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.0447</v>
+        <v>0.5453</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1685</v>
+        <v>-0.0993</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8763</v>
+        <v>0.6446</v>
       </c>
       <c r="G7" t="n">
-        <v>1.0324</v>
+        <v>1.0287</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.4284</v>
+        <v>-0.4389</v>
       </c>
       <c r="I7" t="n">
-        <v>1.4608</v>
+        <v>1.4676</v>
       </c>
       <c r="J7" t="n">
-        <v>0.8209</v>
+        <v>0.7979000000000001</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1865</v>
+        <v>0.1649</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6344</v>
+        <v>0.633</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2115</v>
+        <v>0.2308</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.6149</v>
+        <v>-0.6037</v>
       </c>
       <c r="O7" t="n">
-        <v>0.8264</v>
+        <v>0.8345</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R7" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S7" t="n">
-        <v>1.0519</v>
+        <v>0.5669</v>
       </c>
       <c r="T7" t="n">
-        <v>1.2945</v>
+        <v>1.0636</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2426</v>
+        <v>-0.4967</v>
       </c>
       <c r="V7" t="n">
-        <v>0.3214</v>
+        <v>0.3155</v>
       </c>
       <c r="W7" t="n">
-        <v>0.3214</v>
+        <v>0.3155</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>T. BELL-HAYNES</t>
+          <t>J. RODRIGUEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6986</v>
+        <v>0.4445</v>
       </c>
       <c r="E8" t="n">
-        <v>1.1823</v>
+        <v>-0.1203</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.4837</v>
+        <v>0.5648</v>
       </c>
       <c r="G8" t="n">
-        <v>1.6276</v>
+        <v>-0.5637</v>
       </c>
       <c r="H8" t="n">
-        <v>1.0651</v>
+        <v>-1.4959</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5625</v>
+        <v>0.9322</v>
       </c>
       <c r="J8" t="n">
-        <v>3.6891</v>
+        <v>0.3528</v>
       </c>
       <c r="K8" t="n">
-        <v>3.2067</v>
+        <v>-0.3317</v>
       </c>
       <c r="L8" t="n">
-        <v>0.4824</v>
+        <v>0.6845</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.0615</v>
+        <v>-0.9164</v>
       </c>
       <c r="N8" t="n">
-        <v>-2.1416</v>
+        <v>-1.1642</v>
       </c>
       <c r="O8" t="n">
-        <v>0.08</v>
+        <v>0.2477</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.4537</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R8" t="n">
-        <v>1.8147</v>
+        <v>1.3658</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.636</v>
+        <v>1.374</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3992</v>
+        <v>1.2586</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2368</v>
+        <v>0.1154</v>
       </c>
       <c r="V8" t="n">
-        <v>0.1607</v>
+        <v>0.5447</v>
       </c>
       <c r="W8" t="n">
-        <v>0.1607</v>
+        <v>0.5447</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>S. YUSTA</t>
+          <t>J. FERNANDEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5202</v>
+        <v>0.2173</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.1786</v>
+        <v>1.6362</v>
       </c>
       <c r="F9" t="n">
-        <v>1.6987</v>
+        <v>-1.4189</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.537</v>
+        <v>0.1258</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1933</v>
+        <v>0.2208</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.7302999999999999</v>
+        <v>-0.0951</v>
       </c>
       <c r="J9" t="n">
-        <v>0.4445</v>
+        <v>0.7122000000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>2.7289</v>
+        <v>0.6378</v>
       </c>
       <c r="L9" t="n">
-        <v>-2.2844</v>
+        <v>0.0745</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.9815</v>
+        <v>-0.5865</v>
       </c>
       <c r="N9" t="n">
-        <v>-2.5356</v>
+        <v>-0.4169</v>
       </c>
       <c r="O9" t="n">
-        <v>1.5541</v>
+        <v>-0.1695</v>
       </c>
       <c r="P9" t="n">
-        <v>-2.4952</v>
+        <v>1.1382</v>
       </c>
       <c r="Q9" t="n">
-        <v>-4.5367</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.0415</v>
+        <v>1.1382</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4969</v>
+        <v>0.5876</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0212</v>
+        <v>0.7662</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.5181</v>
+        <v>-0.1786</v>
       </c>
       <c r="V9" t="n">
-        <v>4.0492</v>
+        <v>-1.6342</v>
       </c>
       <c r="W9" t="n">
-        <v>2.8924</v>
+        <v>0.1578</v>
       </c>
       <c r="X9" t="n">
-        <v>1.1568</v>
+        <v>-1.792</v>
       </c>
     </row>
     <row r="10">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.5082</v>
+        <v>-0.6097</v>
       </c>
       <c r="E10" t="n">
-        <v>0.3171</v>
+        <v>1.1133</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.8253</v>
+        <v>-1.723</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.4807</v>
+        <v>-0.4841</v>
       </c>
       <c r="H10" t="n">
-        <v>-3.8526</v>
+        <v>-3.8597</v>
       </c>
       <c r="I10" t="n">
-        <v>3.3719</v>
+        <v>3.3756</v>
       </c>
       <c r="J10" t="n">
-        <v>0.3655</v>
+        <v>0.331</v>
       </c>
       <c r="K10" t="n">
-        <v>-2.356</v>
+        <v>-2.3797</v>
       </c>
       <c r="L10" t="n">
-        <v>2.7214</v>
+        <v>2.7106</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.8461</v>
+        <v>-0.8149999999999999</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.4966</v>
+        <v>-1.48</v>
       </c>
       <c r="O10" t="n">
-        <v>0.6505</v>
+        <v>0.665</v>
       </c>
       <c r="P10" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.6569</v>
+        <v>0.2323</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0484</v>
+        <v>0.7823</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.6085</v>
+        <v>-0.5501</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>12.7846</v>
+        <v>13.1395</v>
       </c>
       <c r="E11" t="n">
-        <v>14.24</v>
+        <v>14.3046</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.4556</v>
+        <v>-1.1648</v>
       </c>
       <c r="G11" t="n">
-        <v>6.036200000000001</v>
+        <v>6.0265</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.1208</v>
+        <v>-2.152400000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>8.1568</v>
+        <v>8.178900000000001</v>
       </c>
       <c r="J11" t="n">
-        <v>17.2317</v>
+        <v>16.9885</v>
       </c>
       <c r="K11" t="n">
-        <v>11.741</v>
+        <v>11.5695</v>
       </c>
       <c r="L11" t="n">
-        <v>5.490399999999999</v>
+        <v>5.419</v>
       </c>
       <c r="M11" t="n">
-        <v>-11.1954</v>
+        <v>-10.9619</v>
       </c>
       <c r="N11" t="n">
-        <v>-13.8619</v>
+        <v>-13.7217</v>
       </c>
       <c r="O11" t="n">
-        <v>2.6662</v>
+        <v>2.7599</v>
       </c>
       <c r="P11" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0.000100000000000211</v>
       </c>
       <c r="Q11" t="n">
-        <v>-14.7441</v>
+        <v>-14.796</v>
       </c>
       <c r="R11" t="n">
-        <v>14.7442</v>
+        <v>14.7962</v>
       </c>
       <c r="S11" t="n">
-        <v>4.8845</v>
+        <v>5.2498</v>
       </c>
       <c r="T11" t="n">
-        <v>6.5783</v>
+        <v>6.9654</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.6937</v>
+        <v>-1.7159</v>
       </c>
       <c r="V11" t="n">
-        <v>1.8638</v>
+        <v>1.8634</v>
       </c>
       <c r="W11" t="n">
-        <v>5.1742</v>
+        <v>5.1467</v>
       </c>
       <c r="X11" t="n">
-        <v>-3.3103</v>
+        <v>-3.2833</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>3.5507</v>
+        <v>3.193</v>
       </c>
       <c r="E12" t="n">
-        <v>4.586</v>
+        <v>4.0703</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.0353</v>
+        <v>-0.8773</v>
       </c>
       <c r="G12" t="n">
-        <v>1.2253</v>
+        <v>1.214</v>
       </c>
       <c r="H12" t="n">
-        <v>1.8038</v>
+        <v>1.7982</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.5785</v>
+        <v>-0.5842000000000001</v>
       </c>
       <c r="J12" t="n">
-        <v>1.7701</v>
+        <v>1.7305</v>
       </c>
       <c r="K12" t="n">
-        <v>2.8604</v>
+        <v>2.8334</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.0903</v>
+        <v>-1.1029</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.5447</v>
+        <v>-0.5164</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.0566</v>
+        <v>-1.0351</v>
       </c>
       <c r="O12" t="n">
-        <v>0.5118</v>
+        <v>0.5187</v>
       </c>
       <c r="P12" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.1963</v>
+        <v>-0.5446</v>
       </c>
       <c r="T12" t="n">
-        <v>1.0162</v>
+        <v>0.5479000000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.2125</v>
+        <v>-1.0925</v>
       </c>
       <c r="V12" t="n">
-        <v>0.7071</v>
+        <v>0.7025</v>
       </c>
       <c r="W12" t="n">
-        <v>1.7997</v>
+        <v>1.792</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="13">
@@ -1423,58 +1423,58 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.095</v>
+        <v>1.84</v>
       </c>
       <c r="E13" t="n">
-        <v>2.6923</v>
+        <v>2.3331</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.5973000000000001</v>
+        <v>-0.4931</v>
       </c>
       <c r="G13" t="n">
-        <v>1.0888</v>
+        <v>1.091</v>
       </c>
       <c r="H13" t="n">
-        <v>0.8196</v>
+        <v>0.8213</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2692</v>
+        <v>0.2696</v>
       </c>
       <c r="J13" t="n">
-        <v>2.1146</v>
+        <v>2.1079</v>
       </c>
       <c r="K13" t="n">
-        <v>0.8832</v>
+        <v>0.8791</v>
       </c>
       <c r="L13" t="n">
-        <v>1.2315</v>
+        <v>1.2288</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.0258</v>
+        <v>-1.0169</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.0636</v>
+        <v>-0.0578</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.9622000000000001</v>
+        <v>-0.9592000000000001</v>
       </c>
       <c r="P13" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S13" t="n">
-        <v>0.3257</v>
+        <v>0.06619999999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>0.5777</v>
+        <v>0.2252</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2519</v>
+        <v>-0.159</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>K. KUATH</t>
+          <t>A. ALBICY</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,64 +1501,64 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9442</v>
+        <v>0.9495</v>
       </c>
       <c r="E14" t="n">
-        <v>2.6523</v>
+        <v>2.0948</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.7081</v>
+        <v>-1.1453</v>
       </c>
       <c r="G14" t="n">
-        <v>1.6225</v>
+        <v>-0.9077</v>
       </c>
       <c r="H14" t="n">
-        <v>2.4488</v>
+        <v>-0.7421</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.8263</v>
+        <v>-0.1656</v>
       </c>
       <c r="J14" t="n">
-        <v>3.6046</v>
+        <v>1.4574</v>
       </c>
       <c r="K14" t="n">
-        <v>3.5672</v>
+        <v>0.8101</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0373</v>
+        <v>0.6473</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.9821</v>
+        <v>-2.3651</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.1185</v>
+        <v>-1.5522</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.8636</v>
+        <v>-0.8129</v>
       </c>
       <c r="P14" t="n">
-        <v>-1.361</v>
+        <v>0.9105</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.2683</v>
+        <v>-1.1382</v>
       </c>
       <c r="R14" t="n">
-        <v>0.9073</v>
+        <v>2.0487</v>
       </c>
       <c r="S14" t="n">
-        <v>0.522</v>
+        <v>-0.6875</v>
       </c>
       <c r="T14" t="n">
-        <v>1.1553</v>
+        <v>0.1414</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.6333</v>
+        <v>-0.8289</v>
       </c>
       <c r="V14" t="n">
-        <v>0.1607</v>
+        <v>1.6342</v>
       </c>
       <c r="W14" t="n">
-        <v>0.1607</v>
+        <v>1.6342</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>P. PELOS</t>
+          <t>L. LABEYRIE</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5185999999999999</v>
+        <v>0.3693</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.0269</v>
+        <v>3.0632</v>
       </c>
       <c r="F15" t="n">
-        <v>1.5456</v>
+        <v>-2.6939</v>
       </c>
       <c r="G15" t="n">
-        <v>1.3197</v>
+        <v>0.1464</v>
       </c>
       <c r="H15" t="n">
-        <v>2.9004</v>
+        <v>0.9848</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.5807</v>
+        <v>-0.8385</v>
       </c>
       <c r="J15" t="n">
-        <v>1.985</v>
+        <v>2.8826</v>
       </c>
       <c r="K15" t="n">
-        <v>3.0753</v>
+        <v>1.8476</v>
       </c>
       <c r="L15" t="n">
-        <v>-1.0903</v>
+        <v>1.035</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.6653</v>
+        <v>-2.7362</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.1749</v>
+        <v>-0.8628</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.4904</v>
+        <v>-1.8734</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.5878</v>
+        <v>2.0487</v>
       </c>
       <c r="Q15" t="n">
-        <v>-3.4025</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.8147</v>
+        <v>2.0487</v>
       </c>
       <c r="S15" t="n">
-        <v>0.6261</v>
+        <v>-0.7363</v>
       </c>
       <c r="T15" t="n">
-        <v>0.2299</v>
+        <v>0.0229</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3962</v>
+        <v>-0.7592</v>
       </c>
       <c r="V15" t="n">
-        <v>0.1607</v>
+        <v>-1.0895</v>
       </c>
       <c r="W15" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. ALBICY</t>
+          <t>P. PELOS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3509</v>
+        <v>0.1851</v>
       </c>
       <c r="E16" t="n">
-        <v>2.0035</v>
+        <v>-1.0734</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.6526</v>
+        <v>1.2585</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.9222</v>
+        <v>1.3071</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.7622</v>
+        <v>2.8953</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.16</v>
+        <v>-1.5883</v>
       </c>
       <c r="J16" t="n">
-        <v>1.4775</v>
+        <v>1.9513</v>
       </c>
       <c r="K16" t="n">
-        <v>0.8139</v>
+        <v>3.0542</v>
       </c>
       <c r="L16" t="n">
-        <v>0.6636</v>
+        <v>-1.1029</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.3996</v>
+        <v>-0.6442</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.5761</v>
+        <v>-0.1588</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.8236</v>
+        <v>-0.4854</v>
       </c>
       <c r="P16" t="n">
-        <v>0.9073</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1342</v>
+        <v>-3.4145</v>
       </c>
       <c r="R16" t="n">
-        <v>2.0415</v>
+        <v>1.8211</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.2733</v>
+        <v>0.3137</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0212</v>
+        <v>0.232</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.2945</v>
+        <v>0.08160000000000001</v>
       </c>
       <c r="V16" t="n">
-        <v>1.639</v>
+        <v>0.1578</v>
       </c>
       <c r="W16" t="n">
-        <v>1.639</v>
+        <v>0.1578</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>L. LABEYRIE</t>
+          <t>K. KUATH</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2581</v>
+        <v>0.1185</v>
       </c>
       <c r="E17" t="n">
-        <v>3.0872</v>
+        <v>1.683</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.829</v>
+        <v>-1.5645</v>
       </c>
       <c r="G17" t="n">
-        <v>0.1374</v>
+        <v>1.6239</v>
       </c>
       <c r="H17" t="n">
-        <v>0.9797</v>
+        <v>2.4444</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.8423</v>
+        <v>-0.8205</v>
       </c>
       <c r="J17" t="n">
-        <v>2.9053</v>
+        <v>3.588</v>
       </c>
       <c r="K17" t="n">
-        <v>1.8631</v>
+        <v>3.5508</v>
       </c>
       <c r="L17" t="n">
-        <v>1.0422</v>
+        <v>0.0372</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.7679</v>
+        <v>-1.9642</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.8834</v>
+        <v>-1.1064</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.8844</v>
+        <v>-0.8578</v>
       </c>
       <c r="P17" t="n">
-        <v>2.0415</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-2.2763</v>
       </c>
       <c r="R17" t="n">
-        <v>2.0415</v>
+        <v>0.9105</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.8280999999999999</v>
+        <v>-0.2973</v>
       </c>
       <c r="T17" t="n">
-        <v>0.0212</v>
+        <v>0.2135</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.8493000000000001</v>
+        <v>-0.5108</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.0927</v>
+        <v>0.1578</v>
       </c>
       <c r="W17" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.2534</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.8137</v>
+        <v>-1.7268</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.7846</v>
+        <v>-1.6839</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.029</v>
+        <v>-0.043</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.6718</v>
+        <v>-1.6721</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.9596</v>
+        <v>-1.9534</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2878</v>
+        <v>0.2812</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.041</v>
+        <v>-1.0539</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.6998</v>
+        <v>-0.7035</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.3413</v>
+        <v>-0.3505</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.6308</v>
+        <v>-0.6182</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.2599</v>
+        <v>-1.2499</v>
       </c>
       <c r="O18" t="n">
-        <v>0.6291</v>
+        <v>0.6317</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R18" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S18" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.1729</v>
       </c>
       <c r="T18" t="n">
-        <v>0.2299</v>
+        <v>0.3505</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1449</v>
+        <v>-0.1775</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="19">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.5738</v>
+        <v>-2.4727</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.9072</v>
+        <v>-1.0393</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.6666</v>
+        <v>-1.4334</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.9033</v>
+        <v>-0.9026</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.7936</v>
+        <v>-1.795</v>
       </c>
       <c r="I19" t="n">
-        <v>0.8903</v>
+        <v>0.8924</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.0725</v>
+        <v>-0.0844</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.7069</v>
+        <v>-0.7174</v>
       </c>
       <c r="L19" t="n">
-        <v>0.6344</v>
+        <v>0.633</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.8308</v>
+        <v>-0.8182</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.0867</v>
+        <v>-1.0775</v>
       </c>
       <c r="O19" t="n">
-        <v>0.2559</v>
+        <v>0.2593</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R19" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.6025</v>
+        <v>-0.5018</v>
       </c>
       <c r="T19" t="n">
-        <v>0.2994</v>
+        <v>0.1833</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.9019</v>
+        <v>-0.6851</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="20">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.5824</v>
+        <v>-2.6677</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.7184</v>
+        <v>-1.8064</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.864</v>
+        <v>-0.8613</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.0696</v>
+        <v>-2.0722</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.3637</v>
+        <v>-0.362</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.706</v>
+        <v>-1.7103</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.6798999999999999</v>
+        <v>-0.7097</v>
       </c>
       <c r="K20" t="n">
-        <v>1.0075</v>
+        <v>0.989</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.6874</v>
+        <v>-1.6987</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.3897</v>
+        <v>-1.3626</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.3711</v>
+        <v>-1.351</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.0186</v>
+        <v>-0.0116</v>
       </c>
       <c r="P20" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R20" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.645</v>
+        <v>-0.7352</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.9043</v>
+        <v>0.0414</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.7407</v>
+        <v>-0.7766</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.3214</v>
+        <v>-0.3155</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.3214</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="21">
@@ -2047,58 +2047,58 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-6.1725</v>
+        <v>-5.7515</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.9673</v>
+        <v>-4.4123</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.2052</v>
+        <v>-1.3392</v>
       </c>
       <c r="G21" t="n">
-        <v>-3.328</v>
+        <v>-3.3322</v>
       </c>
       <c r="H21" t="n">
-        <v>0.1559</v>
+        <v>0.1551</v>
       </c>
       <c r="I21" t="n">
-        <v>-3.4839</v>
+        <v>-3.4873</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.7996</v>
+        <v>-0.8233</v>
       </c>
       <c r="K21" t="n">
-        <v>1.4475</v>
+        <v>1.4339</v>
       </c>
       <c r="L21" t="n">
-        <v>-2.2471</v>
+        <v>-2.2572</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.5284</v>
+        <v>-2.5089</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.2917</v>
+        <v>-1.2788</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.2368</v>
+        <v>-1.2301</v>
       </c>
       <c r="P21" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="Q21" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5762</v>
+        <v>-0.1429</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.7652</v>
+        <v>-0.1745</v>
       </c>
       <c r="U21" t="n">
-        <v>0.189</v>
+        <v>0.0316</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-6.3598</v>
+        <v>-6.0383</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.1613</v>
+        <v>-2.0643</v>
       </c>
       <c r="F22" t="n">
-        <v>-4.1985</v>
+        <v>-3.974</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.5349</v>
+        <v>-2.5221</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.1084</v>
+        <v>-2.0945</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.4265</v>
+        <v>-0.4276</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.0684</v>
+        <v>-0.08450000000000001</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.2495</v>
+        <v>-0.2553</v>
       </c>
       <c r="L22" t="n">
-        <v>0.1812</v>
+        <v>0.1708</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.4665</v>
+        <v>-2.4376</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.8588</v>
+        <v>-1.8392</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.6077</v>
+        <v>-0.5984</v>
       </c>
       <c r="P22" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R22" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.322</v>
+        <v>-1.0186</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1875</v>
+        <v>-0.0678</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.1345</v>
+        <v>-0.9509</v>
       </c>
       <c r="V22" t="n">
-        <v>-2.9566</v>
+        <v>-2.9529</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.7712</v>
+        <v>-0.7739</v>
       </c>
       <c r="X22" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="23">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-12.7847</v>
+        <v>-12.0016</v>
       </c>
       <c r="E23" t="n">
-        <v>1.455600000000003</v>
+        <v>1.164799999999999</v>
       </c>
       <c r="F23" t="n">
-        <v>-14.24</v>
+        <v>-13.1665</v>
       </c>
       <c r="G23" t="n">
-        <v>-6.0361</v>
+        <v>-6.0265</v>
       </c>
       <c r="H23" t="n">
-        <v>2.1207</v>
+        <v>2.1521</v>
       </c>
       <c r="I23" t="n">
-        <v>-8.1569</v>
+        <v>-8.1791</v>
       </c>
       <c r="J23" t="n">
-        <v>11.1957</v>
+        <v>10.9619</v>
       </c>
       <c r="K23" t="n">
-        <v>13.8619</v>
+        <v>13.7219</v>
       </c>
       <c r="L23" t="n">
-        <v>-2.6662</v>
+        <v>-2.7601</v>
       </c>
       <c r="M23" t="n">
-        <v>-17.2316</v>
+        <v>-16.9885</v>
       </c>
       <c r="N23" t="n">
-        <v>-11.7413</v>
+        <v>-11.5695</v>
       </c>
       <c r="O23" t="n">
-        <v>-5.490500000000001</v>
+        <v>-5.4191</v>
       </c>
       <c r="P23" t="n">
-        <v>0.000199999999999978</v>
+        <v>0.0002000000000008106</v>
       </c>
       <c r="Q23" t="n">
-        <v>-14.7443</v>
+        <v>-14.7963</v>
       </c>
       <c r="R23" t="n">
-        <v>14.7441</v>
+        <v>14.7961</v>
       </c>
       <c r="S23" t="n">
-        <v>-4.884600000000001</v>
+        <v>-4.1114</v>
       </c>
       <c r="T23" t="n">
-        <v>1.6938</v>
+        <v>1.7158</v>
       </c>
       <c r="U23" t="n">
-        <v>-6.5783</v>
+        <v>-5.8273</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.8639</v>
+        <v>-1.8634</v>
       </c>
       <c r="W23" t="n">
-        <v>3.3103</v>
+        <v>3.2835</v>
       </c>
       <c r="X23" t="n">
-        <v>-5.174200000000001</v>
+        <v>-5.1467</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104585_W15.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104585_W15.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X23"/>
+  <dimension ref="A1:Y23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104585_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104585_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104585_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104585_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>1.1609</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104585_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104585_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>0</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104585_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-1.792</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104585_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104585_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,7 @@
       <c r="X11" t="n">
         <v>-3.2833</v>
       </c>
+      <c r="Y11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1458,11 @@
       <c r="X12" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104585_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1541,11 @@
       <c r="X13" t="n">
         <v>0</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104585_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>0</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104585_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104585_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>0</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104585_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104585_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104585_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104585_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104585_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>0</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104585_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104585_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,7 @@
       <c r="X23" t="n">
         <v>-5.1467</v>
       </c>
+      <c r="Y23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
